--- a/M2_Statistica_&_Excel/W1_D4.xlsx
+++ b/M2_Statistica_&_Excel/W1_D4.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FB3E0E-35AA-4B53-8E85-C28E29EDDC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2733BBA5-FE29-4C34-A88E-CC62E1231457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BBAFF6-076A-2245-A83A-B4C0C143B4B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Esercizio 1" sheetId="2" r:id="rId1"/>
+    <sheet name="Esercizi_probabilità" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/M2_Statistica_&_Excel/W1_D4.xlsx
+++ b/M2_Statistica_&_Excel/W1_D4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\esercizi consegnati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2733BBA5-FE29-4C34-A88E-CC62E1231457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79ABF8A-683B-4720-BAC8-9BF9D327C7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BBAFF6-076A-2245-A83A-B4C0C143B4B7}"/>
   </bookViews>
